--- a/data/dividends_info_20260616.xlsx
+++ b/data/dividends_info_20260616.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>66.58000183105469</v>
+        <v>65.68000030517578</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1351757247294361</v>
+        <v>0.1370280139796341</v>
       </c>
       <c r="J2" t="n">
         <v>272</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.40000152587891</v>
+        <v>64.90000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.070336366464775</v>
+        <v>1.078582409155838</v>
       </c>
       <c r="J3" t="n">
         <v>251</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.899999618530273</v>
+        <v>8.920000076293945</v>
       </c>
       <c r="I4" t="n">
-        <v>0.674157332266361</v>
+        <v>0.6726457341570856</v>
       </c>
       <c r="J4" t="n">
         <v>181</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>66.56999969482422</v>
+        <v>65.68000030517578</v>
       </c>
       <c r="I6" t="n">
-        <v>0.135196034869439</v>
+        <v>0.1370280139796341</v>
       </c>
       <c r="J6" t="n">
         <v>181</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.075000047683716</v>
+        <v>2.079999923706055</v>
       </c>
       <c r="I7" t="n">
-        <v>3.710843288218411</v>
+        <v>3.701923212708811</v>
       </c>
       <c r="J7" t="n">
         <v>160</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22.20999908447266</v>
+        <v>22.01000022888184</v>
       </c>
       <c r="I8" t="n">
-        <v>1.215668667851324</v>
+        <v>1.226715116729995</v>
       </c>
       <c r="J8" t="n">
         <v>160</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.400000095367432</v>
+        <v>7.349999904632568</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8108108003614941</v>
+        <v>0.8163265412042129</v>
       </c>
       <c r="J10" t="n">
         <v>125</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.20999908447266</v>
+        <v>22.01000022888184</v>
       </c>
       <c r="I14" t="n">
-        <v>1.215668667851324</v>
+        <v>1.226715116729995</v>
       </c>
       <c r="J14" t="n">
         <v>97</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>66.56999969482422</v>
+        <v>65.68000030517578</v>
       </c>
       <c r="I15" t="n">
-        <v>0.135196034869439</v>
+        <v>0.1370280139796341</v>
       </c>
       <c r="J15" t="n">
         <v>97</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>5.08474568052218</v>
       </c>
       <c r="J16" t="n">
         <v>90</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.78000020980835</v>
+        <v>5.75</v>
       </c>
       <c r="I19" t="n">
-        <v>4.325259358568248</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="J19" t="n">
         <v>41</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.340000152587891</v>
+        <v>4.320000171661377</v>
       </c>
       <c r="I20" t="n">
-        <v>3.225806338198391</v>
+        <v>3.240740611965279</v>
       </c>
       <c r="J20" t="n">
         <v>34</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.888999938964844</v>
+        <v>9.935000419616699</v>
       </c>
       <c r="I21" t="n">
-        <v>2.629183957980853</v>
+        <v>2.617010458163937</v>
       </c>
       <c r="J21" t="n">
         <v>34</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.76000022888184</v>
+        <v>14.72000026702881</v>
       </c>
       <c r="I22" t="n">
-        <v>4.065040587370328</v>
+        <v>4.076086882579305</v>
       </c>
       <c r="J22" t="n">
         <v>34</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.706000089645386</v>
+        <v>3.721999883651733</v>
       </c>
       <c r="I23" t="n">
-        <v>5.936319338326055</v>
+        <v>5.910800829583942</v>
       </c>
       <c r="J23" t="n">
         <v>34</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.5</v>
+        <v>6.429999828338623</v>
       </c>
       <c r="I25" t="n">
-        <v>1.538461538461539</v>
+        <v>1.555209994863062</v>
       </c>
       <c r="J25" t="n">
         <v>34</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.820000171661377</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I27" t="n">
-        <v>2.061855609288493</v>
+        <v>2.058319066387184</v>
       </c>
       <c r="J27" t="n">
         <v>27</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.819999933242798</v>
+        <v>2.759999990463257</v>
       </c>
       <c r="I29" t="n">
-        <v>5.319149062089187</v>
+        <v>5.434782627474683</v>
       </c>
       <c r="J29" t="n">
         <v>27</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.699999809265137</v>
+        <v>4.559999942779541</v>
       </c>
       <c r="I31" t="n">
-        <v>1.489361762568769</v>
+        <v>1.535087738561058</v>
       </c>
       <c r="J31" t="n">
         <v>20</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>36.25</v>
+        <v>36.15000152587891</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4137931034482759</v>
+        <v>0.4149377418217221</v>
       </c>
       <c r="J32" t="n">
         <v>20</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>22.57999992370605</v>
+        <v>22.6200008392334</v>
       </c>
       <c r="I34" t="n">
-        <v>1.107174494440687</v>
+        <v>1.105216581452932</v>
       </c>
       <c r="J34" t="n">
         <v>6</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>30.54999923706055</v>
+        <v>29.89999961853027</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6382978882809376</v>
+        <v>0.6521739213640337</v>
       </c>
       <c r="J35" t="n">
         <v>6</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.845000028610229</v>
+        <v>1.840000033378601</v>
       </c>
       <c r="I36" t="n">
-        <v>1.788617858442944</v>
+        <v>1.793478228334894</v>
       </c>
       <c r="J36" t="n">
         <v>6</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.460000038146973</v>
+        <v>5.46999979019165</v>
       </c>
       <c r="I37" t="n">
-        <v>5.311355274246863</v>
+        <v>5.301645541559323</v>
       </c>
       <c r="J37" t="n">
         <v>6</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.78600001335144</v>
+        <v>3.793999910354614</v>
       </c>
       <c r="I38" t="n">
-        <v>4.226096128783817</v>
+        <v>4.217185128637635</v>
       </c>
       <c r="J38" t="n">
         <v>6</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.710000038146973</v>
+        <v>2.691999912261963</v>
       </c>
       <c r="I39" t="n">
-        <v>5.11439107191936</v>
+        <v>5.148588577907525</v>
       </c>
       <c r="J39" t="n">
         <v>6</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>52.29000091552734</v>
+        <v>51.70000076293945</v>
       </c>
       <c r="I40" t="n">
-        <v>1.204819256013674</v>
+        <v>1.218568647394698</v>
       </c>
       <c r="J40" t="n">
         <v>6</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.409999847412109</v>
+        <v>6.364999771118164</v>
       </c>
       <c r="I41" t="n">
-        <v>2.184087415486005</v>
+        <v>2.199528751521159</v>
       </c>
       <c r="J41" t="n">
         <v>6</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>18.04999923706055</v>
+        <v>18</v>
       </c>
       <c r="I42" t="n">
-        <v>4.321329822543658</v>
+        <v>4.333333333333334</v>
       </c>
       <c r="J42" t="n">
         <v>6</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>29.06999969482422</v>
+        <v>28.97999954223633</v>
       </c>
       <c r="I43" t="n">
-        <v>2.923976638882932</v>
+        <v>2.933057327213495</v>
       </c>
       <c r="J43" t="n">
         <v>6</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>66.56999969482422</v>
+        <v>65.68000030517578</v>
       </c>
       <c r="I44" t="n">
-        <v>0.135196034869439</v>
+        <v>0.1370280139796341</v>
       </c>
       <c r="J44" t="n">
         <v>6</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.639999985694885</v>
+        <v>1.629999995231628</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6097561028796531</v>
+        <v>0.6134969343100499</v>
       </c>
       <c r="J45" t="n">
         <v>6</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.377999782562256</v>
+        <v>6.401999950408936</v>
       </c>
       <c r="I46" t="n">
-        <v>2.842583979003614</v>
+        <v>2.831927544585802</v>
       </c>
       <c r="J46" t="n">
         <v>6</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.350000381469727</v>
+        <v>9.270000457763672</v>
       </c>
       <c r="I47" t="n">
-        <v>2.780748549650119</v>
+        <v>2.804746355565158</v>
       </c>
       <c r="J47" t="n">
         <v>6</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.25500011444092</v>
+        <v>10.31999969482422</v>
       </c>
       <c r="I48" t="n">
-        <v>2.701121374049848</v>
+        <v>2.684108606504355</v>
       </c>
       <c r="J48" t="n">
         <v>6</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.059999942779541</v>
+        <v>1.065000057220459</v>
       </c>
       <c r="I49" t="n">
-        <v>1.273584974410487</v>
+        <v>1.26760556569674</v>
       </c>
       <c r="J49" t="n">
         <v>-1</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.151999950408936</v>
+        <v>3.124000072479248</v>
       </c>
       <c r="I50" t="n">
-        <v>3.489847770642534</v>
+        <v>3.521126678870482</v>
       </c>
       <c r="J50" t="n">
         <v>-1</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.710000038146973</v>
+        <v>1.700000047683716</v>
       </c>
       <c r="I51" t="n">
-        <v>1.403508740620111</v>
+        <v>1.41176466628342</v>
       </c>
       <c r="J51" t="n">
         <v>-1</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.015000104904175</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="I52" t="n">
-        <v>5.306799152004847</v>
+        <v>5.26315796078077</v>
       </c>
       <c r="J52" t="n">
         <v>-8</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.79999923706055</v>
+        <v>27.64999961853027</v>
       </c>
       <c r="I54" t="n">
-        <v>3.99280586497371</v>
+        <v>4.014466601497197</v>
       </c>
       <c r="J54" t="n">
         <v>-12</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.9120000004768372</v>
+        <v>0.9039999842643738</v>
       </c>
       <c r="I55" t="n">
-        <v>3.289473682490633</v>
+        <v>3.318584128561946</v>
       </c>
       <c r="J55" t="n">
         <v>-15</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.460000038146973</v>
+        <v>9.340000152587891</v>
       </c>
       <c r="I58" t="n">
-        <v>2.114164896337316</v>
+        <v>2.141327588143398</v>
       </c>
       <c r="J58" t="n">
         <v>-15</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.460000038146973</v>
+        <v>2.440000057220459</v>
       </c>
       <c r="I59" t="n">
-        <v>7.31707305726659</v>
+        <v>7.377049007328634</v>
       </c>
       <c r="J59" t="n">
         <v>-22</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>17.18000030517578</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="I61" t="n">
-        <v>1.455180416525854</v>
+        <v>1.461988271479283</v>
       </c>
       <c r="J61" t="n">
         <v>-22</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.990000009536743</v>
+        <v>4.099999904632568</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7518796974510066</v>
+        <v>0.7317073340929389</v>
       </c>
       <c r="J62" t="n">
         <v>-22</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4.400000095367432</v>
+        <v>4.409999847412109</v>
       </c>
       <c r="I63" t="n">
-        <v>3.409090835200855</v>
+        <v>3.401360661906224</v>
       </c>
       <c r="J63" t="n">
         <v>-22</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.69999980926514</v>
+        <v>12.35000038146973</v>
       </c>
       <c r="I64" t="n">
-        <v>4.566929202446662</v>
+        <v>4.696356130241482</v>
       </c>
       <c r="J64" t="n">
         <v>-22</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.269000053405762</v>
+        <v>2.26200008392334</v>
       </c>
       <c r="I65" t="n">
-        <v>4.583516859944377</v>
+        <v>4.597700978844199</v>
       </c>
       <c r="J65" t="n">
         <v>-29</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>10.3100004196167</v>
+        <v>10.34500026702881</v>
       </c>
       <c r="I66" t="n">
-        <v>2.812802989301735</v>
+        <v>2.803286539530375</v>
       </c>
       <c r="J66" t="n">
         <v>-29</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>42.41999816894531</v>
+        <v>42.65000152587891</v>
       </c>
       <c r="I68" t="n">
-        <v>3.866101062683698</v>
+        <v>3.845251914011986</v>
       </c>
       <c r="J68" t="n">
         <v>-29</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>37.84999847412109</v>
+        <v>38.04999923706055</v>
       </c>
       <c r="I69" t="n">
-        <v>5.284016065066543</v>
+        <v>5.256241892514963</v>
       </c>
       <c r="J69" t="n">
         <v>-29</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3.25600004196167</v>
+        <v>3.334000110626221</v>
       </c>
       <c r="I70" t="n">
-        <v>3.071253031672327</v>
+        <v>2.999400020452223</v>
       </c>
       <c r="J70" t="n">
         <v>-29</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>36.77999877929688</v>
+        <v>35.56000137329102</v>
       </c>
       <c r="I71" t="n">
-        <v>0.4036432977903381</v>
+        <v>0.417491547431457</v>
       </c>
       <c r="J71" t="n">
         <v>-29</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>21.95999908447266</v>
+        <v>22.1200008392334</v>
       </c>
       <c r="I72" t="n">
-        <v>4.189435511636738</v>
+        <v>4.159131849435698</v>
       </c>
       <c r="J72" t="n">
         <v>-29</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>11.22000026702881</v>
+        <v>11.1899995803833</v>
       </c>
       <c r="I73" t="n">
-        <v>2.673796727809202</v>
+        <v>2.680965247987291</v>
       </c>
       <c r="J73" t="n">
         <v>-29</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>87.87999725341797</v>
+        <v>87.83999633789062</v>
       </c>
       <c r="I74" t="n">
-        <v>1.183431989649443</v>
+        <v>1.183970905462556</v>
       </c>
       <c r="J74" t="n">
         <v>-29</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>47.40999984741211</v>
+        <v>47.0099983215332</v>
       </c>
       <c r="I75" t="n">
-        <v>1.476481759656048</v>
+        <v>1.489044937232769</v>
       </c>
       <c r="J75" t="n">
         <v>-29</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>65.40000152587891</v>
+        <v>64.90000152587891</v>
       </c>
       <c r="I76" t="n">
-        <v>3.36391429460358</v>
+        <v>3.389830428775489</v>
       </c>
       <c r="J76" t="n">
         <v>-29</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>10.94799995422363</v>
+        <v>10.94999980926514</v>
       </c>
       <c r="I77" t="n">
-        <v>7.855316072304333</v>
+        <v>7.853881415343287</v>
       </c>
       <c r="J77" t="n">
         <v>-29</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>13.67599964141846</v>
+        <v>13.64200019836426</v>
       </c>
       <c r="I78" t="n">
-        <v>4.094764658402094</v>
+        <v>4.10496988606661</v>
       </c>
       <c r="J78" t="n">
         <v>-29</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>2.410000085830688</v>
+        <v>2.430000066757202</v>
       </c>
       <c r="I79" t="n">
-        <v>1.659750978233374</v>
+        <v>1.646090489757862</v>
       </c>
       <c r="J79" t="n">
         <v>-29</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>9.930000305175781</v>
+        <v>10</v>
       </c>
       <c r="I80" t="n">
-        <v>3.021147943405722</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
         <v>-29</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>93.40000152587891</v>
+        <v>92.30000305175781</v>
       </c>
       <c r="I82" t="n">
-        <v>2.205567415787701</v>
+        <v>2.231852580595086</v>
       </c>
       <c r="J82" t="n">
         <v>-29</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>16.67000007629395</v>
+        <v>16.73999977111816</v>
       </c>
       <c r="I83" t="n">
-        <v>4.499100159372879</v>
+        <v>4.480286799609097</v>
       </c>
       <c r="J83" t="n">
         <v>-29</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>15.60999965667725</v>
+        <v>15.35999965667725</v>
       </c>
       <c r="I84" t="n">
-        <v>1.921845013440943</v>
+        <v>1.953125043655747</v>
       </c>
       <c r="J84" t="n">
         <v>-29</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>50.40000152587891</v>
+        <v>49.20000076293945</v>
       </c>
       <c r="I85" t="n">
-        <v>1.686507885448278</v>
+        <v>1.72764224963239</v>
       </c>
       <c r="J85" t="n">
         <v>-29</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>38.31999969482422</v>
+        <v>38.2400016784668</v>
       </c>
       <c r="I86" t="n">
-        <v>2.218162856913611</v>
+        <v>2.22280324971492</v>
       </c>
       <c r="J86" t="n">
         <v>-29</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>66.68000030517578</v>
+        <v>66.44000244140625</v>
       </c>
       <c r="I87" t="n">
-        <v>1.949610069061581</v>
+        <v>1.956652547005061</v>
       </c>
       <c r="J87" t="n">
         <v>-29</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>7.5</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="I88" t="n">
-        <v>8</v>
+        <v>8.21917786744058</v>
       </c>
       <c r="J88" t="n">
         <v>-29</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>23.44000053405762</v>
+        <v>23.3799991607666</v>
       </c>
       <c r="I91" t="n">
-        <v>4.266211506894081</v>
+        <v>4.277160119312901</v>
       </c>
       <c r="J91" t="n">
         <v>-29</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>4.949999809265137</v>
+        <v>5</v>
       </c>
       <c r="I92" t="n">
-        <v>4.343434510796846</v>
+        <v>4.3</v>
       </c>
       <c r="J92" t="n">
         <v>-29</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>22.20999908447266</v>
+        <v>22.01000022888184</v>
       </c>
       <c r="I93" t="n">
-        <v>1.215668667851324</v>
+        <v>1.226715116729995</v>
       </c>
       <c r="J93" t="n">
         <v>-29</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>9.350000381469727</v>
+        <v>9.430000305175781</v>
       </c>
       <c r="I95" t="n">
-        <v>2.566844815061648</v>
+        <v>2.545068846586068</v>
       </c>
       <c r="J95" t="n">
         <v>-29</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>22.6299991607666</v>
+        <v>22.6200008392334</v>
       </c>
       <c r="I96" t="n">
-        <v>3.490941357919337</v>
+        <v>3.492484397391267</v>
       </c>
       <c r="J96" t="n">
         <v>-29</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5.360000133514404</v>
+        <v>5.28000020980835</v>
       </c>
       <c r="I97" t="n">
-        <v>1.735074583645998</v>
+        <v>1.761363566373337</v>
       </c>
       <c r="J97" t="n">
         <v>-29</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>7.400000095367432</v>
+        <v>7.349999904632568</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8108108003614941</v>
+        <v>0.8163265412042129</v>
       </c>
       <c r="J98" t="n">
         <v>-29</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>35.70000076293945</v>
+        <v>35.88000106811523</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9803921359109288</v>
+        <v>0.9754737725217837</v>
       </c>
       <c r="J99" t="n">
         <v>-29</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>6.630000114440918</v>
+        <v>6.739999771118164</v>
       </c>
       <c r="I100" t="n">
-        <v>8.360482510289398</v>
+        <v>8.224035887586414</v>
       </c>
       <c r="J100" t="n">
         <v>-29</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>2.289999961853027</v>
+        <v>2.319999933242798</v>
       </c>
       <c r="I101" t="n">
-        <v>2.620087379890132</v>
+        <v>2.58620697096894</v>
       </c>
       <c r="J101" t="n">
         <v>-29</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>13.64999961853027</v>
+        <v>13.60000038146973</v>
       </c>
       <c r="I102" t="n">
-        <v>1.465201506148719</v>
+        <v>1.47058819404523</v>
       </c>
       <c r="J102" t="n">
         <v>-29</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>7.5</v>
+        <v>7.474999904632568</v>
       </c>
       <c r="I103" t="n">
-        <v>1.373333333333333</v>
+        <v>1.377926438984522</v>
       </c>
       <c r="J103" t="n">
         <v>-29</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>6.01800012588501</v>
+        <v>6.056000232696533</v>
       </c>
       <c r="I104" t="n">
-        <v>3.157195015379939</v>
+        <v>3.137384291601974</v>
       </c>
       <c r="J104" t="n">
         <v>-29</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>10.52999973297119</v>
+        <v>10.54500007629395</v>
       </c>
       <c r="I105" t="n">
-        <v>4.10256420660046</v>
+        <v>4.096728277614456</v>
       </c>
       <c r="J105" t="n">
         <v>-29</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>26.88999938964844</v>
+        <v>26.29000091552734</v>
       </c>
       <c r="I106" t="n">
-        <v>1.636296057966376</v>
+        <v>1.673640109080895</v>
       </c>
       <c r="J106" t="n">
         <v>-29</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>6.920000076293945</v>
+        <v>6.849999904632568</v>
       </c>
       <c r="I108" t="n">
-        <v>6.791907439569159</v>
+        <v>6.861313964138086</v>
       </c>
       <c r="J108" t="n">
         <v>-29</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>54.41999816894531</v>
+        <v>53.88000106811523</v>
       </c>
       <c r="I109" t="n">
-        <v>2.572583695526304</v>
+        <v>2.598366689395786</v>
       </c>
       <c r="J109" t="n">
         <v>-29</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.5</v>
+        <v>3.552999973297119</v>
       </c>
       <c r="I110" t="n">
-        <v>8.571428571428571</v>
+        <v>8.44356887854422</v>
       </c>
       <c r="J110" t="n">
         <v>-29</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>15.69999980926514</v>
+        <v>15.64999961853027</v>
       </c>
       <c r="I111" t="n">
-        <v>0.7643312194767268</v>
+        <v>0.7667731816294413</v>
       </c>
       <c r="J111" t="n">
         <v>-29</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>3.319999933242798</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="I112" t="n">
-        <v>5.120482030671402</v>
+        <v>5.105105222068654</v>
       </c>
       <c r="J112" t="n">
         <v>-29</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>23.04999923706055</v>
+        <v>22.79999923706055</v>
       </c>
       <c r="I113" t="n">
-        <v>3.036876456266935</v>
+        <v>3.070175541331493</v>
       </c>
       <c r="J113" t="n">
         <v>-29</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>2.779999971389771</v>
+        <v>2.839999914169312</v>
       </c>
       <c r="I114" t="n">
-        <v>1.258992818712257</v>
+        <v>1.232394403442697</v>
       </c>
       <c r="J114" t="n">
         <v>-29</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>5.510000228881836</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="I115" t="n">
-        <v>5.989110459020218</v>
+        <v>6.04395600172919</v>
       </c>
       <c r="J115" t="n">
         <v>-29</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.9309999942779541</v>
+        <v>0.9350000023841858</v>
       </c>
       <c r="I116" t="n">
-        <v>7.518797038692698</v>
+        <v>7.486630996952387</v>
       </c>
       <c r="J116" t="n">
         <v>-29</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>50.75</v>
+        <v>50.59999847412109</v>
       </c>
       <c r="I117" t="n">
-        <v>1.399014778325123</v>
+        <v>1.403162097649317</v>
       </c>
       <c r="J117" t="n">
         <v>-29</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>101.6999969482422</v>
+        <v>100.8000030517578</v>
       </c>
       <c r="I118" t="n">
-        <v>1.327433668151485</v>
+        <v>1.339285673738338</v>
       </c>
       <c r="J118" t="n">
         <v>-29</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>4.683000087738037</v>
+        <v>4.596000194549561</v>
       </c>
       <c r="I121" t="n">
-        <v>3.630151544201928</v>
+        <v>3.6988684248013</v>
       </c>
       <c r="J121" t="n">
         <v>-29</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>60.29999923706055</v>
+        <v>59.90000152587891</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7462686661585043</v>
+        <v>0.7512520676741289</v>
       </c>
       <c r="J123" t="n">
         <v>-29</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>5.78000020980835</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6920414973709197</v>
+        <v>0.6872852030961643</v>
       </c>
       <c r="J124" t="n">
         <v>-29</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>38.02000045776367</v>
+        <v>38.09999847412109</v>
       </c>
       <c r="I125" t="n">
-        <v>2.761704332871965</v>
+        <v>2.755905622183156</v>
       </c>
       <c r="J125" t="n">
         <v>-29</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>17.48999977111816</v>
+        <v>17.14999961853027</v>
       </c>
       <c r="I127" t="n">
-        <v>2.172670125630916</v>
+        <v>2.215743489518313</v>
       </c>
       <c r="J127" t="n">
         <v>-29</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>26.68000030517578</v>
+        <v>26.13999938964844</v>
       </c>
       <c r="I128" t="n">
-        <v>2.248875536495414</v>
+        <v>2.295332876853864</v>
       </c>
       <c r="J128" t="n">
         <v>-29</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>36.29999923706055</v>
+        <v>35.75</v>
       </c>
       <c r="I129" t="n">
-        <v>0.9641873480886106</v>
+        <v>0.979020979020979</v>
       </c>
       <c r="J129" t="n">
         <v>-29</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>3.259999990463257</v>
+        <v>3.200000047683716</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5214723941635424</v>
+        <v>0.5312499920837582</v>
       </c>
       <c r="J130" t="n">
         <v>-29</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>24.54999923706055</v>
+        <v>24.46999931335449</v>
       </c>
       <c r="I132" t="n">
-        <v>4.562118268049695</v>
+        <v>4.577033230192043</v>
       </c>
       <c r="J132" t="n">
         <v>-29</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>9.579999923706055</v>
+        <v>9.640000343322754</v>
       </c>
       <c r="I134" t="n">
-        <v>2.71398749551783</v>
+        <v>2.697095339629232</v>
       </c>
       <c r="J134" t="n">
         <v>-29</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2.424000024795532</v>
+        <v>2.401999950408936</v>
       </c>
       <c r="I135" t="n">
-        <v>3.807755736627338</v>
+        <v>3.84263122005003</v>
       </c>
       <c r="J135" t="n">
         <v>-29</v>
@@ -8609,78 +8609,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Directa SIM S.P.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sesa S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>